--- a/miomio/后台升级表格/起运国仓/暂缓/执行任务-执行-合并执行.xlsx
+++ b/miomio/后台升级表格/起运国仓/暂缓/执行任务-执行-合并执行.xlsx
@@ -1,15 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowHeight="18320"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -176,13 +189,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -221,6 +234,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,12 +247,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Microsoft JhengHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
@@ -255,10 +268,34 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -271,10 +308,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -286,11 +323,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -302,10 +339,33 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -318,7 +378,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,68 +392,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -451,19 +464,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -475,37 +554,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -517,43 +608,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -565,67 +632,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -659,10 +672,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -692,88 +725,9 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -797,7 +751,31 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -816,153 +794,188 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -976,13 +989,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -994,28 +1013,40 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1024,28 +1055,46 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1054,109 +1103,73 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1191,7 +1204,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4486910" y="0"/>
+          <a:off x="3888740" y="0"/>
           <a:ext cx="685800" cy="190500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1225,7 +1238,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1677035" y="0"/>
+          <a:off x="1453515" y="0"/>
           <a:ext cx="685800" cy="180975"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1501,9 +1514,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:J31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="2" max="2" width="13.0083333333333" customWidth="1"/>
+    <col min="2" max="2" width="13.0096153846154" customWidth="1"/>
     <col min="3" max="3" width="11.625" customWidth="1"/>
     <col min="4" max="4" width="13.625" customWidth="1"/>
     <col min="5" max="6" width="11.625" customWidth="1"/>
@@ -1522,727 +1535,727 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="34"/>
+      <c r="J2" s="3"/>
     </row>
     <row r="3" ht="25" customHeight="1" spans="2:10">
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="35"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="6"/>
     </row>
     <row r="4" ht="25" customHeight="1" spans="2:10">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="37"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="12"/>
     </row>
     <row r="5" ht="25" customHeight="1" spans="2:10">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="11" t="s">
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="38"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="16"/>
     </row>
     <row r="6" ht="25" customHeight="1" spans="2:10">
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="15" t="s">
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="15"/>
-      <c r="J6" s="39"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="21"/>
     </row>
     <row r="7" ht="25" customHeight="1" spans="2:10">
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="40" t="s">
+      <c r="J7" s="25" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1" spans="2:10">
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="28">
         <v>0.872</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="28">
         <v>145.25</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="28">
         <v>1323</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="28">
         <v>1323</v>
       </c>
-      <c r="I8" s="41">
+      <c r="I8" s="29">
         <v>1</v>
       </c>
-      <c r="J8" s="42" t="s">
+      <c r="J8" s="30" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1" spans="2:10">
-      <c r="B9" s="19"/>
-      <c r="C9" s="22" t="s">
+      <c r="B9" s="26"/>
+      <c r="C9" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="32">
         <v>0.12</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="32">
         <v>20</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="32">
         <v>1954</v>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="32">
         <v>1954</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="31">
         <v>1</v>
       </c>
-      <c r="J9" s="43" t="s">
+      <c r="J9" s="33" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="2:10">
-      <c r="B10" s="19"/>
-      <c r="C10" s="20" t="s">
+      <c r="B10" s="26"/>
+      <c r="C10" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="28">
         <v>0.24</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="28">
         <v>40</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="28">
         <v>31.44</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H10" s="28">
         <v>31.44</v>
       </c>
-      <c r="I10" s="41">
+      <c r="I10" s="29">
         <v>1</v>
       </c>
-      <c r="J10" s="42" t="s">
+      <c r="J10" s="30" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1" spans="2:10">
-      <c r="B11" s="19"/>
-      <c r="C11" s="22" t="s">
+      <c r="B11" s="26"/>
+      <c r="C11" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="32">
         <v>0.06</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="32">
         <v>10.051</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="32">
         <v>176</v>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="32">
         <v>176</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="31">
         <v>1</v>
       </c>
-      <c r="J11" s="43" t="s">
+      <c r="J11" s="33" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1" spans="2:10">
-      <c r="B12" s="19"/>
-      <c r="C12" s="20" t="s">
+      <c r="B12" s="26"/>
+      <c r="C12" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="28">
         <v>0.336</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="28">
         <v>56</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="28">
         <v>152</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="28">
         <v>152</v>
       </c>
-      <c r="I12" s="41">
+      <c r="I12" s="29">
         <v>1</v>
       </c>
-      <c r="J12" s="42" t="s">
+      <c r="J12" s="30" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1" spans="2:10">
-      <c r="B13" s="19"/>
-      <c r="C13" s="22" t="s">
+      <c r="B13" s="26"/>
+      <c r="C13" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="32">
         <v>0.872</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="32">
         <v>145.25</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="32">
         <v>489</v>
       </c>
-      <c r="H13" s="23">
+      <c r="H13" s="32">
         <v>489</v>
       </c>
-      <c r="I13" s="22">
+      <c r="I13" s="31">
         <v>1</v>
       </c>
-      <c r="J13" s="43" t="s">
+      <c r="J13" s="33" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1" spans="2:10">
-      <c r="B14" s="19"/>
-      <c r="C14" s="20" t="s">
+      <c r="B14" s="26"/>
+      <c r="C14" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="28">
         <v>0.12</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="28">
         <v>20</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="28">
         <v>145.25</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="28">
         <v>145.25</v>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="29">
         <v>1</v>
       </c>
-      <c r="J14" s="42" t="s">
+      <c r="J14" s="30" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1" spans="2:10">
-      <c r="B15" s="19"/>
-      <c r="C15" s="22" t="s">
+      <c r="B15" s="26"/>
+      <c r="C15" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="32">
         <v>0.24</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="32">
         <v>40</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="32">
         <v>20</v>
       </c>
-      <c r="H15" s="23">
+      <c r="H15" s="32">
         <v>20</v>
       </c>
-      <c r="I15" s="22">
+      <c r="I15" s="31">
         <v>1</v>
       </c>
-      <c r="J15" s="43" t="s">
+      <c r="J15" s="33" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1" spans="2:10">
-      <c r="B16" s="19"/>
-      <c r="C16" s="20" t="s">
+      <c r="B16" s="26"/>
+      <c r="C16" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="28">
         <v>0.06</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="28">
         <v>10.051</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="28">
         <v>40</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="28">
         <v>40</v>
       </c>
-      <c r="I16" s="41">
+      <c r="I16" s="29">
         <v>1</v>
       </c>
-      <c r="J16" s="42" t="s">
+      <c r="J16" s="30" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1" spans="2:10">
-      <c r="B17" s="19"/>
-      <c r="C17" s="22" t="s">
+      <c r="B17" s="26"/>
+      <c r="C17" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="32">
         <v>0.336</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="32">
         <v>56</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="32">
         <v>10.051</v>
       </c>
-      <c r="H17" s="23">
+      <c r="H17" s="32">
         <v>10.051</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="31">
         <v>1</v>
       </c>
-      <c r="J17" s="43" t="s">
+      <c r="J17" s="33" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1" spans="2:10">
-      <c r="B18" s="19"/>
-      <c r="C18" s="20" t="s">
+      <c r="B18" s="26"/>
+      <c r="C18" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="28">
         <v>0.872</v>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="28">
         <v>145.25</v>
       </c>
-      <c r="G18" s="21">
+      <c r="G18" s="28">
         <v>1323</v>
       </c>
-      <c r="H18" s="21">
+      <c r="H18" s="28">
         <v>1323</v>
       </c>
-      <c r="I18" s="41">
+      <c r="I18" s="29">
         <v>1</v>
       </c>
-      <c r="J18" s="42" t="s">
+      <c r="J18" s="30" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" ht="25" customHeight="1" spans="2:10">
-      <c r="B19" s="19"/>
-      <c r="C19" s="22" t="s">
+      <c r="B19" s="26"/>
+      <c r="C19" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="32">
         <v>0.12</v>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="32">
         <v>20</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="32">
         <v>1954</v>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="32">
         <v>1954</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19" s="31">
         <v>1</v>
       </c>
-      <c r="J19" s="43" t="s">
+      <c r="J19" s="33" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="20" ht="25" customHeight="1" spans="2:10">
-      <c r="B20" s="19"/>
-      <c r="C20" s="20" t="s">
+      <c r="B20" s="26"/>
+      <c r="C20" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="28">
         <v>0.24</v>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="28">
         <v>40</v>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="28">
         <v>31.44</v>
       </c>
-      <c r="H20" s="21">
+      <c r="H20" s="28">
         <v>31.44</v>
       </c>
-      <c r="I20" s="41">
+      <c r="I20" s="29">
         <v>1</v>
       </c>
-      <c r="J20" s="42" t="s">
+      <c r="J20" s="30" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="2:10">
-      <c r="B21" s="19"/>
-      <c r="C21" s="22" t="s">
+      <c r="B21" s="26"/>
+      <c r="C21" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="32">
         <v>0.06</v>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="32">
         <v>10.051</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="32">
         <v>176</v>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="32">
         <v>176</v>
       </c>
-      <c r="I21" s="22">
+      <c r="I21" s="31">
         <v>1</v>
       </c>
-      <c r="J21" s="43" t="s">
+      <c r="J21" s="33" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1" spans="2:10">
-      <c r="B22" s="19"/>
-      <c r="C22" s="20" t="s">
+      <c r="B22" s="26"/>
+      <c r="C22" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="28">
         <v>0.336</v>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="28">
         <v>56</v>
       </c>
-      <c r="G22" s="21">
+      <c r="G22" s="28">
         <v>152</v>
       </c>
-      <c r="H22" s="21">
+      <c r="H22" s="28">
         <v>152</v>
       </c>
-      <c r="I22" s="41">
+      <c r="I22" s="29">
         <v>1</v>
       </c>
-      <c r="J22" s="42" t="s">
+      <c r="J22" s="30" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="2:10">
-      <c r="B23" s="19"/>
-      <c r="C23" s="22" t="s">
+      <c r="B23" s="26"/>
+      <c r="C23" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="32">
         <v>0.872</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="32">
         <v>145.25</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="32">
         <v>489</v>
       </c>
-      <c r="H23" s="23">
+      <c r="H23" s="32">
         <v>489</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23" s="31">
         <v>1</v>
       </c>
-      <c r="J23" s="43" t="s">
+      <c r="J23" s="33" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1" spans="2:10">
-      <c r="B24" s="19"/>
-      <c r="C24" s="20" t="s">
+      <c r="B24" s="26"/>
+      <c r="C24" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="28">
         <v>0.12</v>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="28">
         <v>20</v>
       </c>
-      <c r="G24" s="21">
+      <c r="G24" s="28">
         <v>145.25</v>
       </c>
-      <c r="H24" s="21">
+      <c r="H24" s="28">
         <v>145.25</v>
       </c>
-      <c r="I24" s="41">
+      <c r="I24" s="29">
         <v>1</v>
       </c>
-      <c r="J24" s="42" t="s">
+      <c r="J24" s="30" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1" spans="2:10">
-      <c r="B25" s="19"/>
-      <c r="C25" s="22" t="s">
+      <c r="B25" s="26"/>
+      <c r="C25" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="D25" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="23">
+      <c r="E25" s="32">
         <v>0.24</v>
       </c>
-      <c r="F25" s="23">
+      <c r="F25" s="32">
         <v>40</v>
       </c>
-      <c r="G25" s="23">
+      <c r="G25" s="32">
         <v>20</v>
       </c>
-      <c r="H25" s="23">
+      <c r="H25" s="32">
         <v>20</v>
       </c>
-      <c r="I25" s="22">
+      <c r="I25" s="31">
         <v>1</v>
       </c>
-      <c r="J25" s="43" t="s">
+      <c r="J25" s="33" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1" spans="2:10">
-      <c r="B26" s="19"/>
-      <c r="C26" s="20" t="s">
+      <c r="B26" s="26"/>
+      <c r="C26" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="28">
         <v>0.06</v>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="28">
         <v>10.051</v>
       </c>
-      <c r="G26" s="21">
+      <c r="G26" s="28">
         <v>40</v>
       </c>
-      <c r="H26" s="21">
+      <c r="H26" s="28">
         <v>40</v>
       </c>
-      <c r="I26" s="41">
+      <c r="I26" s="29">
         <v>1</v>
       </c>
-      <c r="J26" s="42" t="s">
+      <c r="J26" s="30" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1" spans="2:10">
-      <c r="B27" s="19"/>
-      <c r="C27" s="22" t="s">
+      <c r="B27" s="26"/>
+      <c r="C27" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="D27" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="32">
         <v>0.336</v>
       </c>
-      <c r="F27" s="23">
+      <c r="F27" s="32">
         <v>56</v>
       </c>
-      <c r="G27" s="23">
+      <c r="G27" s="32">
         <v>10.051</v>
       </c>
-      <c r="H27" s="23">
+      <c r="H27" s="32">
         <v>10.051</v>
       </c>
-      <c r="I27" s="22">
+      <c r="I27" s="31">
         <v>1</v>
       </c>
-      <c r="J27" s="43" t="s">
+      <c r="J27" s="33" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1" spans="2:10">
-      <c r="B28" s="24"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="26">
+      <c r="B28" s="34"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="36">
         <f>SUM(E8:E27)</f>
         <v>6.512</v>
       </c>
-      <c r="F28" s="26">
+      <c r="F28" s="36">
         <f>SUM(F8:F27)</f>
         <v>1085.204</v>
       </c>
-      <c r="G28" s="26">
+      <c r="G28" s="36">
         <f>SUM(G8:G27)</f>
         <v>8681.482</v>
       </c>
-      <c r="H28" s="26">
+      <c r="H28" s="36">
         <f>SUM(H8:H27)</f>
         <v>8681.482</v>
       </c>
-      <c r="I28" s="30">
+      <c r="I28" s="37">
         <f>SUM(I8:I27)</f>
         <v>20</v>
       </c>
-      <c r="J28" s="44"/>
+      <c r="J28" s="38"/>
     </row>
     <row r="29" ht="25" customHeight="1" spans="2:10">
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="28" t="s">
+      <c r="D29" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="E29" s="28" t="s">
+      <c r="E29" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28" t="s">
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="I29" s="28" t="s">
+      <c r="I29" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="J29" s="45" t="s">
+      <c r="J29" s="41" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1" spans="2:10">
-      <c r="B30" s="29"/>
-      <c r="C30" s="30" t="s">
+      <c r="B30" s="42"/>
+      <c r="C30" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="31">
+      <c r="D30" s="43">
         <v>13570217212</v>
       </c>
-      <c r="E30" s="31" t="s">
+      <c r="E30" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31" t="s">
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="I30" s="31" t="s">
+      <c r="I30" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="J30" s="46" t="s">
+      <c r="J30" s="44" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1" spans="2:10">
-      <c r="B31" s="32" t="s">
+      <c r="B31" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="33"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="33"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="10">
